--- a/artfynd/A 33548-2025 artfynd.xlsx
+++ b/artfynd/A 33548-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>131274492</v>
       </c>
       <c r="B3" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33548-2025 artfynd.xlsx
+++ b/artfynd/A 33548-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>131274492</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>57728</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33548-2025 artfynd.xlsx
+++ b/artfynd/A 33548-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>131274492</v>
       </c>
       <c r="B3" t="n">
-        <v>57733</v>
+        <v>57739</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33548-2025 artfynd.xlsx
+++ b/artfynd/A 33548-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>131274492</v>
       </c>
       <c r="B3" t="n">
-        <v>57739</v>
+        <v>57740</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33548-2025 artfynd.xlsx
+++ b/artfynd/A 33548-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>131274492</v>
       </c>
       <c r="B3" t="n">
-        <v>57740</v>
+        <v>57743</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
